--- a/diseases/d058/2005-2009.xlsx
+++ b/diseases/d058/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -1357,9 +1354,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -1801,9 +1795,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2236,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -2689,9 +2677,6 @@
       <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -3133,9 +3118,6 @@
       <c r="O18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01880813123160408</v>
       </c>
@@ -3577,9 +3559,6 @@
       <c r="O21" t="n">
         <v>7</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -4021,9 +4000,6 @@
       <c r="O24" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.0104489617953356</v>
       </c>
@@ -4465,9 +4441,6 @@
       <c r="O27" t="n">
         <v>24</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.05015501661761088</v>
       </c>
@@ -4909,9 +4882,6 @@
       <c r="O30" t="n">
         <v>2159</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>4.511861703225912</v>
       </c>
@@ -5353,9 +5323,6 @@
       <c r="O33" t="n">
         <v>4167</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>8.708164760232689</v>
       </c>
@@ -5797,9 +5764,6 @@
       <c r="O36" t="n">
         <v>390</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.8150190200361769</v>
       </c>
@@ -6241,9 +6205,6 @@
       <c r="O39" t="n">
         <v>11</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.02291355543546769</v>
       </c>
@@ -6685,9 +6646,6 @@
       <c r="O42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -7129,9 +7087,6 @@
       <c r="O45" t="n">
         <v>4</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.008332201976533707</v>
       </c>
@@ -7573,9 +7528,6 @@
       <c r="O48" t="n">
         <v>13</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.02707965642373455</v>
       </c>
@@ -8017,9 +7969,6 @@
       <c r="O51" t="n">
         <v>8</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01666440395306741</v>
       </c>
@@ -8461,9 +8410,6 @@
       <c r="O54" t="n">
         <v>9</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.01874745444720084</v>
       </c>
@@ -8905,9 +8851,6 @@
       <c r="O57" t="n">
         <v>5</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.01041525247066713</v>
       </c>
@@ -9349,9 +9292,6 @@
       <c r="O60" t="n">
         <v>5</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.01041525247066713</v>
       </c>
@@ -9793,9 +9733,6 @@
       <c r="O63" t="n">
         <v>29</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.06040846432986937</v>
       </c>
@@ -10237,9 +10174,6 @@
       <c r="O66" t="n">
         <v>2054</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>4.278585714950059</v>
       </c>
@@ -10681,9 +10615,6 @@
       <c r="O69" t="n">
         <v>3766</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>7.844768160906485</v>
       </c>
@@ -11125,9 +11056,6 @@
       <c r="O72" t="n">
         <v>573</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.193587933138454</v>
       </c>
@@ -11569,9 +11497,6 @@
       <c r="O75" t="n">
         <v>25</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.05189077693019498</v>
       </c>
@@ -12013,9 +11938,6 @@
       <c r="O78" t="n">
         <v>10</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.02075631077207799</v>
       </c>
@@ -12457,9 +12379,6 @@
       <c r="O81" t="n">
         <v>6</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.01245378646324679</v>
       </c>
@@ -12901,9 +12820,6 @@
       <c r="O84" t="n">
         <v>11</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.02283194184928579</v>
       </c>
@@ -13345,9 +13261,6 @@
       <c r="O87" t="n">
         <v>13</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.02698320400370139</v>
       </c>
@@ -13789,9 +13702,6 @@
       <c r="O90" t="n">
         <v>17</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.03528572831253259</v>
       </c>
@@ -14233,9 +14143,6 @@
       <c r="O93" t="n">
         <v>12</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.02490757292649359</v>
       </c>
@@ -14677,9 +14584,6 @@
       <c r="O96" t="n">
         <v>11</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.02283194184928579</v>
       </c>
@@ -15121,9 +15025,6 @@
       <c r="O99" t="n">
         <v>26</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.05396640800740277</v>
       </c>
@@ -15565,9 +15466,6 @@
       <c r="O102" t="n">
         <v>1123</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>2.330933699704358</v>
       </c>
@@ -16009,9 +15907,6 @@
       <c r="O105" t="n">
         <v>4374</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>9.078810331706913</v>
       </c>
@@ -16453,9 +16348,6 @@
       <c r="O108" t="n">
         <v>394</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.8177986444198728</v>
       </c>
@@ -16897,9 +16789,6 @@
       <c r="O111" t="n">
         <v>14</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.02895164461161399</v>
       </c>
@@ -17341,9 +17230,6 @@
       <c r="O114" t="n">
         <v>10</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.02067974615115285</v>
       </c>
@@ -17785,9 +17671,6 @@
       <c r="O117" t="n">
         <v>2</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -18229,9 +18112,6 @@
       <c r="O120" t="n">
         <v>8</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.01654379692092229</v>
       </c>
@@ -18673,9 +18553,6 @@
       <c r="O123" t="n">
         <v>22</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.04549544153253628</v>
       </c>
@@ -19117,9 +18994,6 @@
       <c r="O126" t="n">
         <v>8</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01654379692092229</v>
       </c>
@@ -19561,9 +19435,6 @@
       <c r="O129" t="n">
         <v>12</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.02481569538138343</v>
       </c>
@@ -20005,9 +19876,6 @@
       <c r="O132" t="n">
         <v>6</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -20449,9 +20317,6 @@
       <c r="O135" t="n">
         <v>38</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.07858303537438086</v>
       </c>
@@ -20893,9 +20758,6 @@
       <c r="O138" t="n">
         <v>3035</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>6.276302956874892</v>
       </c>
@@ -21337,9 +21199,6 @@
       <c r="O141" t="n">
         <v>2547</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>5.267131344698632</v>
       </c>
@@ -21781,9 +21640,6 @@
       <c r="O144" t="n">
         <v>355</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.7341309883659264</v>
       </c>
@@ -22225,9 +22081,6 @@
       <c r="O147" t="n">
         <v>39</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.08033503996199617</v>
       </c>
@@ -22669,9 +22522,6 @@
       <c r="O150" t="n">
         <v>17</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.03501783793215218</v>
       </c>
@@ -23113,9 +22963,6 @@
       <c r="O153" t="n">
         <v>13</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.02677834665399872</v>
       </c>
@@ -23557,9 +23404,6 @@
       <c r="O156" t="n">
         <v>15</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.03089809229307545</v>
       </c>
@@ -24001,9 +23845,6 @@
       <c r="O159" t="n">
         <v>14</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.02883821947353709</v>
       </c>
@@ -24445,9 +24286,6 @@
       <c r="O162" t="n">
         <v>21</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.04325732921030563</v>
       </c>
@@ -24889,9 +24727,6 @@
       <c r="O165" t="n">
         <v>14</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.02883821947353709</v>
       </c>
@@ -25333,9 +25168,6 @@
       <c r="O168" t="n">
         <v>12</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.02471847383446036</v>
       </c>
@@ -25777,9 +25609,6 @@
       <c r="O171" t="n">
         <v>51</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1050535137964565</v>
       </c>
@@ -26221,9 +26050,6 @@
       <c r="O174" t="n">
         <v>1739</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>3.582118833177213</v>
       </c>
@@ -26665,9 +26491,6 @@
       <c r="O177" t="n">
         <v>2641</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>5.440124116400817</v>
       </c>
@@ -27108,9 +26931,6 @@
       </c>
       <c r="O180" t="n">
         <v>419</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0.8630867113865741</v>
